--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487821_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487821_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9228</v>
+        <v>10.3183</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3756</v>
+        <v>9.0059</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5472</v>
+        <v>1.3123</v>
       </c>
       <c r="G2" t="n">
         <v>4.5943</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5367</v>
+        <v>1.9321</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8542</v>
+        <v>1.4845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6825</v>
+        <v>0.4476</v>
       </c>
       <c r="V2" t="n">
         <v>2.3351</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.6232</v>
+        <v>7.9923</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0025</v>
+        <v>4.9606</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6207</v>
+        <v>3.0317</v>
       </c>
       <c r="G3" t="n">
         <v>8.2125</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6518</v>
+        <v>-0.2827</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0743</v>
+        <v>0.0324</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7261</v>
+        <v>-0.3151</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3538</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ROYO ARGOTE</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5616</v>
+        <v>2.6039</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1593</v>
+        <v>2.6258</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7209</v>
+        <v>-0.0218</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0035</v>
+        <v>3.4832</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9619</v>
+        <v>3.8122</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0416</v>
+        <v>-0.329</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2212</v>
+        <v>4.3978</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3454</v>
+        <v>4.8738</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5666</v>
+        <v>-0.476</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2247</v>
+        <v>-0.9146</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6165</v>
+        <v>-1.0616</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6082</v>
+        <v>0.147</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0812</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3555</v>
+        <v>0.8294</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0619</v>
+        <v>0.663</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4175</v>
+        <v>0.1664</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1675</v>
+        <v>-0.4599</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-0.1061</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>I. ROYO ARGOTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4721</v>
+        <v>2.1586</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7984</v>
+        <v>-0.4155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6737</v>
+        <v>2.5741</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8173</v>
+        <v>2.0035</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5756</v>
+        <v>1.9619</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2417</v>
+        <v>0.0416</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4788</v>
+        <v>-0.2212</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2044</v>
+        <v>0.3454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2743</v>
+        <v>-0.5666</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6614</v>
+        <v>2.2247</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6288</v>
+        <v>1.6165</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0326</v>
+        <v>0.6082</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.0812</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8223</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3602</v>
+        <v>-0.1943</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4621</v>
+        <v>-0.5643</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1675</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.879</v>
+        <v>1.6056</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9595</v>
+        <v>1.9586</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0806</v>
+        <v>-0.353</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4832</v>
+        <v>1.1102</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8122</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.329</v>
+        <v>1.2058</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3978</v>
+        <v>1.5594</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8738</v>
+        <v>-0.1771</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.476</v>
+        <v>1.7365</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9146</v>
+        <v>-0.4492</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0616</v>
+        <v>0.0814</v>
       </c>
       <c r="O6" t="n">
-        <v>0.147</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1044</v>
+        <v>0.9762</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0033</v>
+        <v>0.753</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1077</v>
+        <v>0.2232</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4599</v>
+        <v>-1.5213</v>
       </c>
       <c r="W6" t="n">
         <v>-0.3538</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1061</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5213</v>
+        <v>1.5383</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7862</v>
+        <v>1.3931</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2649</v>
+        <v>0.1453</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1102</v>
+        <v>0.8173</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.5756</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2058</v>
+        <v>0.2417</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5594</v>
+        <v>1.4788</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1771</v>
+        <v>1.2044</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7365</v>
+        <v>0.2743</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4492</v>
+        <v>-0.6614</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0814</v>
+        <v>-0.6288</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.0326</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8919</v>
+        <v>1.8885</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5806</v>
+        <v>0.9549</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3113</v>
+        <v>0.9336</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5213</v>
+        <v>-1.1675</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-1.1675</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8122</v>
+        <v>1.3816</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5537</v>
+        <v>-1.1018</v>
       </c>
       <c r="F8" t="n">
-        <v>2.366</v>
+        <v>2.4834</v>
       </c>
       <c r="G8" t="n">
         <v>1.172</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7542</v>
+        <v>-0.1848</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0576</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2446</v>
+        <v>-0.1272</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7622</v>
+        <v>-0.7351</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9529</v>
+        <v>-2.1019</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1906</v>
+        <v>1.3668</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8516</v>
@@ -1234,13 +1234,13 @@
         <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1164</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4005</v>
+        <v>0.2515</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3112</v>
+        <v>-0.135</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5624</v>
+        <v>-3.1627</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7148</v>
+        <v>-5.2536</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1524</v>
+        <v>2.0909</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0084</v>
+        <v>-0.7025</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5863</v>
+        <v>0.5671</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4221</v>
+        <v>-1.2695</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6368</v>
+        <v>-1.3146</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.676</v>
+        <v>0.1019</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0392</v>
+        <v>-1.4165</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3716</v>
+        <v>0.6122</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0897</v>
+        <v>0.4652</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4613</v>
+        <v>0.147</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9137</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1218</v>
+        <v>-4.1624</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0672</v>
+        <v>0.2672</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2486</v>
+        <v>0.2234</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3158</v>
+        <v>0.0438</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7076</v>
+        <v>-0.23</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.717</v>
+        <v>-4.583</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4556</v>
+        <v>-4.5005</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7386</v>
+        <v>-0.0825</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7025</v>
+        <v>-1.0084</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5671</v>
+        <v>-0.5863</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2695</v>
+        <v>-0.4221</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3146</v>
+        <v>-0.6368</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1019</v>
+        <v>-0.676</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4165</v>
+        <v>0.0392</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6122</v>
+        <v>-0.3716</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4652</v>
+        <v>0.0897</v>
       </c>
       <c r="O12" t="n">
-        <v>0.147</v>
+        <v>-0.4613</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4974</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.1624</v>
+        <v>-3.1218</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2872</v>
+        <v>0.0467</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9786</v>
+        <v>-0.0343</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3085</v>
+        <v>0.0809</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.1208</v>
+        <v>-5.5095</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.3819</v>
+        <v>-5.8881</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2612</v>
+        <v>0.3786</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7669</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6889</v>
+        <v>-0.0776</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3791</v>
+        <v>0.1148</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3099</v>
+        <v>-0.1924</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5838</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.7727</v>
+        <v>13.7512</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2960000000000003</v>
+        <v>0.6826000000000016</v>
       </c>
       <c r="F14" t="n">
         <v>13.0687</v>
@@ -1525,10 +1525,10 @@
         <v>10.84</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7347</v>
+        <v>1.734699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6319</v>
+        <v>3.631899999999999</v>
       </c>
       <c r="N14" t="n">
         <v>1.1007</v>
@@ -1546,19 +1546,19 @@
         <v>13.5276</v>
       </c>
       <c r="S14" t="n">
-        <v>3.774299999999999</v>
+        <v>4.7528</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2125</v>
+        <v>4.191299999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5616000000000001</v>
+        <v>0.5614999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-4.0863</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5661</v>
+        <v>0.5660999999999998</v>
       </c>
       <c r="X14" t="n">
         <v>-4.6524</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>P. SANCHEZ INFANTES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7556</v>
+        <v>3.6684</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7067</v>
+        <v>2.6495</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0489</v>
+        <v>1.0189</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0616</v>
+        <v>2.4541</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1898</v>
+        <v>-0.7846</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2515</v>
+        <v>3.2387</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3712</v>
+        <v>3.0258</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0554</v>
+        <v>0.8974</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6842</v>
+        <v>2.1284</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4328</v>
+        <v>-0.5717</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8655</v>
+        <v>-1.6821</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4327</v>
+        <v>1.1104</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
         <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>2.196</v>
+        <v>-0.41</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3355</v>
+        <v>0.0805</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1396</v>
+        <v>-0.4906</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4599</v>
+        <v>0.5838</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6877</v>
+        <v>3.537</v>
       </c>
       <c r="E16" t="n">
         <v>2.6756</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0121</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.849</v>
@@ -1702,13 +1702,13 @@
         <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0125</v>
+        <v>-1.1632</v>
       </c>
       <c r="T16" t="n">
         <v>-0.5004999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.512</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0.3538</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. SANCHEZ INFANTES</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1938</v>
+        <v>2.4697</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4352</v>
+        <v>1.4209</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.0489</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4541</v>
+        <v>-0.0616</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7846</v>
+        <v>0.1898</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2387</v>
+        <v>-0.2515</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0258</v>
+        <v>0.3712</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8974</v>
+        <v>1.0554</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1284</v>
+        <v>-0.6842</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5717</v>
+        <v>-0.4328</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6821</v>
+        <v>-0.8655</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1104</v>
+        <v>0.4327</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8847</v>
+        <v>0.9101</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1338</v>
+        <v>1.0497</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7509</v>
+        <v>-0.1396</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5838</v>
+        <v>-0.4599</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9981</v>
+        <v>2.0759</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0109</v>
+        <v>2.118</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0128</v>
+        <v>-0.0421</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1311</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1885</v>
+        <v>0.2663</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0619</v>
+        <v>0.1691</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1266</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>2.565</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0785</v>
+        <v>-0.0594</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7238</v>
+        <v>-0.6167</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6454</v>
+        <v>0.5573</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2183</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.214</v>
+        <v>-0.1949</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0183</v>
+        <v>-0.1063</v>
       </c>
       <c r="V19" t="n">
         <v>0.3538</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8928</v>
+        <v>-2.1451</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0902</v>
+        <v>-1.6616</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8026</v>
+        <v>-0.4835</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2924</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0166</v>
+        <v>-1.2689</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0191</v>
+        <v>-0.5905</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.6785</v>
       </c>
       <c r="V20" t="n">
         <v>1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2643</v>
+        <v>-2.684</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.974</v>
+        <v>-2.331</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2903</v>
+        <v>-0.353</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6711</v>
@@ -2092,13 +2092,13 @@
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.28</v>
+        <v>-0.6997</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1496</v>
+        <v>-0.5067</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1304</v>
+        <v>-0.193</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3922</v>
+        <v>-4.1588</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3551</v>
+        <v>-2.0336</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0371</v>
+        <v>-2.1252</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7242</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9812</v>
+        <v>-0.7478</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7829</v>
+        <v>-0.4615</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1983</v>
+        <v>-0.2864</v>
       </c>
       <c r="V22" t="n">
         <v>0.3538</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0729</v>
+        <v>-5.1888</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0785</v>
+        <v>-6.4</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0056</v>
+        <v>1.2111</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6107</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0967</v>
+        <v>0.9807</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9968</v>
+        <v>0.6754</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0998</v>
+        <v>0.3054</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4776</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.707100000000001</v>
+        <v>-9.5731</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.6754</v>
+        <v>-8.889699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0317</v>
+        <v>-0.6833</v>
       </c>
       <c r="G24" t="n">
         <v>-6.8001</v>
@@ -2326,13 +2326,13 @@
         <v>1.6649</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.7323</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1743</v>
+        <v>-0.3886</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6922</v>
+        <v>-0.3438</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5838</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.7726</v>
+        <v>-12.0582</v>
       </c>
       <c r="E25" t="n">
         <v>-13.0686</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2961</v>
+        <v>1.0105</v>
       </c>
       <c r="G25" t="n">
         <v>-16.2064</v>
@@ -2404,13 +2404,13 @@
         <v>16.6494</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.774199999999999</v>
+        <v>-3.059699999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-0.5616999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2128</v>
+        <v>-2.4984</v>
       </c>
       <c r="V25" t="n">
         <v>4.0864</v>
